--- a/docs/Lab03/Solutions/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Solutions/Lab03_WBT_TCs_Form.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80820FA8-AEDD-4D4D-97DD-78935686E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E26D9-4703-4B42-A4F9-04DD1D44CC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14745" yWindow="255" windowWidth="13695" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -13,17 +13,28 @@
     <sheet name="F02.TCs" sheetId="11" r:id="rId3"/>
     <sheet name="WBT-TCs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="140">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -104,9 +115,6 @@
   </si>
   <si>
     <t>Req02_L03</t>
-  </si>
-  <si>
-    <t>..</t>
   </si>
   <si>
     <t>F02. Individual Paths</t>
@@ -584,6 +592,42 @@
   </si>
   <si>
     <t>toate</t>
+  </si>
+  <si>
+    <t>F02_TC03</t>
+  </si>
+  <si>
+    <t>F02_TC04</t>
+  </si>
+  <si>
+    <t>F02_TC05</t>
+  </si>
+  <si>
+    <t>F02_TC06</t>
+  </si>
+  <si>
+    <t>nr ing</t>
+  </si>
+  <si>
+    <t>cantitate ceruta</t>
+  </si>
+  <si>
+    <t>stoc in repo</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>F02_TC07</t>
+  </si>
+  <si>
+    <t>5 si 3</t>
+  </si>
+  <si>
+    <t>10 si 10</t>
   </si>
 </sst>
 </file>
@@ -805,7 +849,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1260,6 +1304,45 @@
       </right>
       <top/>
       <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1286,12 +1369,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1354,213 +1431,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1568,11 +1438,224 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1750,8 +1833,8 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>67320</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="4" name="Ink 3">
@@ -1770,7 +1853,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="4" name="Ink 3">
@@ -1815,8 +1898,8 @@
       <xdr:row>42</xdr:row>
       <xdr:rowOff>151920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -1835,7 +1918,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -2215,26 +2298,26 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="39" t="s">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="38" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2244,97 +2327,97 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="35" t="s">
+      <c r="N5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27" t="s">
+      <c r="N6" s="25"/>
+      <c r="O6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="27" t="s">
+      <c r="P6" s="25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="27" t="s">
+      <c r="N7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="P7" s="27">
+      <c r="O7" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="P7" s="25">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="27" t="s">
+      <c r="N8" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="P8" s="27">
+      <c r="O8" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="P8" s="25">
         <v>232</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="27" t="s">
+      <c r="N9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="P9" s="27">
+      <c r="O9" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="P9" s="25">
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="108" t="s">
-        <v>99</v>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
     </row>
   </sheetData>
@@ -2352,452 +2435,459 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:T24"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="39" t="s">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="41"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="45" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B3" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="48"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="I6" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="Q6" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="44"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B8" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="I8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="58"/>
+      <c r="S8" s="58"/>
+      <c r="T8" s="32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B9" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="47"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="39" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="I9" s="35"/>
+      <c r="Q9" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="58"/>
+      <c r="S9" s="58"/>
+      <c r="T9" s="32" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B10" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="I10" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="50"/>
+      <c r="O10" s="51"/>
+      <c r="Q10" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="58"/>
+      <c r="T10" s="32" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B11" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="54"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B12" s="33">
+        <v>4</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="54"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B13" s="33">
+        <v>5</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="54"/>
+      <c r="Q13" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" s="44"/>
+      <c r="S13" s="44"/>
+      <c r="T13" s="44"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B14" s="33">
+        <v>6</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="54"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B15" s="33">
+        <v>7</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="54"/>
+      <c r="Q15" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="S15" s="59"/>
+      <c r="T15" s="59"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B16" s="33">
+        <v>8</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="53"/>
+      <c r="K16" s="53"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="54"/>
+      <c r="Q16" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" s="33">
+        <v>9</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="54"/>
+      <c r="Q17" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B18" s="33">
+        <v>10</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="53"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="54"/>
+      <c r="Q18" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B19" s="33">
+        <v>11</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="54"/>
+      <c r="Q19" s="33">
+        <v>4</v>
+      </c>
+      <c r="R19" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B20" s="33">
         <v>12</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="I6" s="39" t="s">
+      <c r="C20" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="54"/>
+      <c r="Q20" s="33">
+        <v>5</v>
+      </c>
+      <c r="R20" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B21" s="33">
         <v>13</v>
       </c>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="Q6" s="39" t="s">
+      <c r="C21" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="54"/>
+      <c r="Q21" s="33">
+        <v>6</v>
+      </c>
+      <c r="R21" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B22" s="33">
         <v>14</v>
       </c>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="s">
+      <c r="C22" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="54"/>
+      <c r="Q22" s="33">
+        <v>7</v>
+      </c>
+      <c r="R22" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B23" s="33">
         <v>15</v>
       </c>
-      <c r="C8" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="I8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q8" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="R8" s="44"/>
-      <c r="S8" s="44"/>
-      <c r="T8" s="34">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="I9" s="37"/>
-      <c r="Q9" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="I10" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="49"/>
-      <c r="O10" s="50"/>
-      <c r="Q10" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="R10" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="S10" s="44"/>
-      <c r="T10" s="34" t="s">
+      <c r="C23" s="42" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B11" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="53"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" s="35">
-        <v>4</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="53"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B13" s="35">
-        <v>5</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="52"/>
-      <c r="O13" s="53"/>
-      <c r="Q13" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="40"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B14" s="35">
-        <v>6</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="53"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B15" s="35">
-        <v>7</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="53"/>
-      <c r="Q15" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="57"/>
-      <c r="T15" s="57"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B16" s="35">
-        <v>8</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="53"/>
-      <c r="Q16" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="R16" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="35">
-        <v>9</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="53"/>
-      <c r="Q17" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B18" s="35">
-        <v>10</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="53"/>
-      <c r="Q18" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="R18" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B19" s="35">
-        <v>11</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="52"/>
-      <c r="O19" s="53"/>
-      <c r="Q19" s="35">
-        <v>4</v>
-      </c>
-      <c r="R19" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B20" s="35">
-        <v>12</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="53"/>
-      <c r="Q20" s="35">
-        <v>5</v>
-      </c>
-      <c r="R20" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B21" s="35">
-        <v>13</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="52"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="52"/>
-      <c r="O21" s="53"/>
-      <c r="Q21" s="35">
-        <v>6</v>
-      </c>
-      <c r="R21" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B22" s="35">
-        <v>14</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="52"/>
-      <c r="O22" s="53"/>
-      <c r="Q22" s="35">
-        <v>7</v>
-      </c>
-      <c r="R22" s="106" t="s">
-        <v>98</v>
-      </c>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="35">
-        <v>15</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="52"/>
-      <c r="O23" s="53"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="I24" s="54"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="56"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="54"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I24" s="55"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
@@ -2814,19 +2904,12 @@
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2840,597 +2923,612 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:AC17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="6.44140625" customWidth="1"/>
     <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" customWidth="1"/>
-    <col min="16" max="17" width="8.85546875" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" customWidth="1"/>
-    <col min="23" max="25" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.88671875" customWidth="1"/>
+    <col min="16" max="17" width="8.88671875" customWidth="1"/>
+    <col min="22" max="22" width="9.109375" customWidth="1"/>
+    <col min="23" max="25" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="39" t="s">
+    <row r="1" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B3" s="107" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47"/>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
-      <c r="B5" s="11"/>
-    </row>
-    <row r="6" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="64" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B3" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B5" s="9"/>
+    </row>
+    <row r="6" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="64" t="s">
+      <c r="D6" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="65" t="s">
+      <c r="E6" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="64" t="s">
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
+      <c r="V6" s="61"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="61"/>
+      <c r="Z6" s="61"/>
+      <c r="AA6" s="61"/>
+      <c r="AB6" s="61"/>
+      <c r="AC6" s="61"/>
+    </row>
+    <row r="7" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="64"/>
-      <c r="U6" s="64"/>
-      <c r="V6" s="64"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="64"/>
-      <c r="Y6" s="64"/>
-      <c r="Z6" s="64"/>
-      <c r="AA6" s="64"/>
-      <c r="AB6" s="64"/>
-      <c r="AC6" s="64"/>
-    </row>
-    <row r="7" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="61" t="s">
+      <c r="F7" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="60" t="s">
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="62" t="s">
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="65"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="62"/>
-      <c r="U7" s="62"/>
-      <c r="V7" s="62"/>
-      <c r="W7" s="63" t="s">
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="64"/>
+      <c r="AB7" s="64"/>
+      <c r="AC7" s="64"/>
+    </row>
+    <row r="8" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="61"/>
+      <c r="C8" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="71"/>
+      <c r="F8" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="O8" s="68"/>
+      <c r="P8" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="S8" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="T8" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="U8" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="V8" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="W8" s="69">
+        <v>0</v>
+      </c>
+      <c r="X8" s="64">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="64">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="X7" s="63"/>
-      <c r="Y7" s="63"/>
-      <c r="Z7" s="63"/>
-      <c r="AA7" s="63"/>
-      <c r="AB7" s="63"/>
-      <c r="AC7" s="63"/>
-    </row>
-    <row r="8" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="64"/>
-      <c r="C8" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60" t="s">
+      <c r="AA8" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8" s="64" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC8" s="64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="61"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="65"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="64"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="64"/>
+      <c r="AC9" s="64"/>
+    </row>
+    <row r="10" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="O8" s="60"/>
-      <c r="P8" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q8" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="62" t="s">
+      <c r="F10" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+    </row>
+    <row r="11" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+    </row>
+    <row r="12" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="12">
+        <v>3</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+    </row>
+    <row r="13" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="12">
+        <v>4</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="S8" s="62" t="s">
+      <c r="D13" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+    </row>
+    <row r="14" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="12">
+        <v>5</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="T8" s="62" t="s">
-        <v>122</v>
-      </c>
-      <c r="U8" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="V8" s="62" t="s">
+      <c r="D14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="O14" s="15"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+    </row>
+    <row r="15" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B15" s="12">
+        <v>6</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="W8" s="111">
-        <v>0</v>
-      </c>
-      <c r="X8" s="63">
+      <c r="D15" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="Y8" s="63">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA8" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB8" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC8" s="63" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="64"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="P9" s="62"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="62"/>
-      <c r="S9" s="62"/>
-      <c r="T9" s="62"/>
-      <c r="U9" s="62"/>
-      <c r="V9" s="62"/>
-      <c r="W9" s="112"/>
-      <c r="X9" s="63"/>
-      <c r="Y9" s="63"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="63"/>
-      <c r="AC9" s="63"/>
-    </row>
-    <row r="10" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16" t="s">
+      <c r="E15" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="18"/>
-      <c r="W10" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="19"/>
-    </row>
-    <row r="11" spans="2:29" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="15" t="b">
+      <c r="H15" s="15"/>
+      <c r="I15" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="V15" s="16"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+    </row>
+    <row r="16" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="12">
+        <v>7</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="18"/>
-      <c r="W11" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-    </row>
-    <row r="12" spans="2:29" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="14">
-        <v>3</v>
-      </c>
-      <c r="C12" s="109" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="110" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="18"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-    </row>
-    <row r="13" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
-        <v>4</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="18"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-    </row>
-    <row r="14" spans="2:29" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="14">
-        <v>5</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="19"/>
-    </row>
-    <row r="15" spans="2:29" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="14">
-        <v>6</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="V15" s="18"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-    </row>
-    <row r="16" spans="2:29" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="14">
-        <v>7</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="E16" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC16" s="19"/>
-    </row>
-    <row r="17" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="20"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC16" s="17"/>
+    </row>
+    <row r="17" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:V7"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -3447,21 +3545,6 @@
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="W7:AC7"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:V7"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3474,423 +3557,455 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:N16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" customWidth="1"/>
+    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="12"/>
-      <c r="D1" s="39" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B1" s="10"/>
+      <c r="D1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="91" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="45"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B3" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="92" t="s">
+      <c r="C4" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="78" t="s">
+      <c r="D4" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="102" t="s">
+      <c r="E4" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="94" t="s">
+      <c r="L4" s="78"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="76"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L4" s="95"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="93"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="97"/>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19">
+        <v>9</v>
+      </c>
+      <c r="C6" s="81" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="21">
-        <v>9</v>
-      </c>
-      <c r="C6" s="98" t="s">
+      <c r="D6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="88"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="19">
+        <v>10</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="104" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="21">
+      <c r="E7" s="19">
+        <v>0</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="19">
+        <v>11</v>
+      </c>
+      <c r="C8" s="81"/>
+      <c r="D8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="19">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19">
+        <v>0</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="19">
+        <v>12</v>
+      </c>
+      <c r="C9" s="81"/>
+      <c r="D9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="19">
+        <v>1</v>
+      </c>
+      <c r="F9" s="19">
+        <v>5</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B10" s="110">
+        <v>13</v>
+      </c>
+      <c r="C10" s="81"/>
+      <c r="D10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="110">
+        <v>1</v>
+      </c>
+      <c r="F10" s="110">
         <v>10</v>
       </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="4" t="s">
+      <c r="G10" s="110">
+        <v>5</v>
+      </c>
+      <c r="H10" s="110"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B11" s="110">
+        <v>14</v>
+      </c>
+      <c r="C11" s="81"/>
+      <c r="D11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="110">
+        <v>1</v>
+      </c>
+      <c r="F11" s="110">
+        <v>5</v>
+      </c>
+      <c r="G11" s="110">
+        <v>20</v>
+      </c>
+      <c r="H11" s="110"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="112"/>
+      <c r="K11" s="110" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>15</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K14" s="21"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="21">
-        <v>5</v>
-      </c>
-      <c r="F7" s="21">
-        <v>6</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="95"/>
-      <c r="K7" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="21">
-        <v>11</v>
-      </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="21">
-        <v>12</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
-        <v>13</v>
-      </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="23"/>
-    </row>
-    <row r="13" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="83" t="s">
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="75" t="s">
+      <c r="G15" s="91"/>
+      <c r="H15" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="76"/>
-      <c r="H13" s="83" t="s">
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="89" t="s">
+      <c r="N15" s="101"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="N13" s="90"/>
-    </row>
-    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="67" t="s">
+      <c r="C16" s="104" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="D16" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="E16" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="71" t="s">
+      <c r="F16" s="108" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="G16" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="77" t="s">
+      <c r="H16" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="79" t="s">
+      <c r="I16" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" s="81" t="s">
+      <c r="L16" s="96" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="86" t="s">
+      <c r="M16" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="M14" s="88" t="s">
+      <c r="N16" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="N14" s="78" t="s">
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="99"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="94"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="92"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="25">
+        <v>7</v>
+      </c>
+      <c r="C18" s="22">
+        <v>7</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0</v>
+      </c>
+      <c r="E18" s="23"/>
+      <c r="F18" s="24">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="68"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="73"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="27">
-        <f>SUM(C16:D16)</f>
+      <c r="H18" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="25">
+        <f>SUM(J18:K18)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="24">
+      <c r="J18" s="22">
         <v>0</v>
       </c>
-      <c r="D16" s="24">
+      <c r="K18" s="26">
         <v>0</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="27">
-        <f>SUM(J16:K16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="24">
-        <v>0</v>
-      </c>
-      <c r="K16" s="28">
-        <v>0</v>
-      </c>
-      <c r="L16" s="29"/>
-      <c r="M16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="N16" s="30">
-        <f>C16</f>
-        <v>0</v>
+      <c r="L18" s="27"/>
+      <c r="M18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="N18" s="28">
+        <f>C18</f>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="C6:C12"/>
     <mergeCell ref="E4:J4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I12:J12"/>
     <mergeCell ref="I8:J8"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3906,17 +4021,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="08d9df77a39a0ee87f79f9436c57bbce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" xmlns:ns3="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="03dd79bc1474883a2d909db85c328b07" ns2:_="" ns3:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -4105,6 +4209,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
   <ds:schemaRefs>
@@ -4114,17 +4229,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B359A3C-84EA-4FDD-BB5C-023A91F35CC6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4141,4 +4245,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/Lab03/Solutions/Lab03_WBT_TCs_Form.xlsx
+++ b/docs/Lab03/Solutions/Lab03_WBT_TCs_Form.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E26D9-4703-4B42-A4F9-04DD1D44CC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2547AD47-EF26-1146-B67D-B50839B6E4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -1405,7 +1405,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1438,65 +1437,98 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1510,28 +1542,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1540,6 +1572,39 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1570,9 +1635,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1594,69 +1656,7 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2298,26 +2298,26 @@
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P20"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="15" max="15" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B2" s="35" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2327,97 +2327,97 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25" t="s">
+      <c r="N6" s="24"/>
+      <c r="O6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="P6" s="25" t="s">
+      <c r="P6" s="24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="24">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="25" t="s">
+      <c r="O8" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="24">
         <v>232</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="25" t="s">
+      <c r="N9" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="O9" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="P9" s="25">
+      <c r="P9" s="24">
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="36" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
     </row>
   </sheetData>
@@ -2435,459 +2435,453 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:T24"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="17" max="17" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="44"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B3" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="48"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="43" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="50"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="I6" s="43" t="s">
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="I6" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="Q6" s="43" t="s">
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="Q6" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B8" s="30" t="s">
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B8" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
       <c r="I8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="58" t="s">
+      <c r="Q8" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="32">
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="31">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="I9" s="35"/>
-      <c r="Q9" s="58" t="s">
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="I9" s="34"/>
+      <c r="Q9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="R9" s="58"/>
-      <c r="S9" s="58"/>
-      <c r="T9" s="32" t="s">
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="31" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="33" t="s">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B10" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="I10" s="49" t="s">
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="I10" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="51"/>
-      <c r="Q10" s="58" t="s">
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="53"/>
+      <c r="Q10" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="58" t="s">
+      <c r="R10" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="S10" s="58"/>
-      <c r="T10" s="32" t="s">
+      <c r="S10" s="47"/>
+      <c r="T10" s="31" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B11" s="33" t="s">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B11" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="54"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B12" s="33">
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="56"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B12" s="32">
         <v>4</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="54"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="33">
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="56"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B13" s="32">
         <v>5</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="54"/>
-      <c r="Q13" s="43" t="s">
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="56"/>
+      <c r="Q13" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="R13" s="44"/>
-      <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B14" s="33">
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B14" s="32">
         <v>6</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="54"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="33">
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="56"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B15" s="32">
         <v>7</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="54"/>
-      <c r="Q15" s="30" t="s">
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="56"/>
+      <c r="Q15" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="59" t="s">
+      <c r="R15" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="S15" s="59"/>
-      <c r="T15" s="59"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="33">
+      <c r="S15" s="60"/>
+      <c r="T15" s="60"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B16" s="32">
         <v>8</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="54"/>
-      <c r="Q16" s="33" t="s">
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="56"/>
+      <c r="Q16" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R16" s="41" t="s">
+      <c r="R16" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="33">
+      <c r="S16" s="45"/>
+      <c r="T16" s="45"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B17" s="32">
         <v>9</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="54"/>
-      <c r="Q17" s="33" t="s">
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="56"/>
+      <c r="Q17" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="R17" s="41" t="s">
+      <c r="R17" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="33">
+      <c r="S17" s="45"/>
+      <c r="T17" s="45"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B18" s="32">
         <v>10</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="54"/>
-      <c r="Q18" s="33" t="s">
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="56"/>
+      <c r="Q18" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="R18" s="41" t="s">
+      <c r="R18" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="33">
+      <c r="S18" s="45"/>
+      <c r="T18" s="45"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B19" s="32">
         <v>11</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="54"/>
-      <c r="Q19" s="33">
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="56"/>
+      <c r="Q19" s="32">
         <v>4</v>
       </c>
-      <c r="R19" s="41" t="s">
+      <c r="R19" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="33">
+      <c r="S19" s="45"/>
+      <c r="T19" s="45"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B20" s="32">
         <v>12</v>
       </c>
-      <c r="C20" s="42" t="s">
+      <c r="C20" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="54"/>
-      <c r="Q20" s="33">
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="56"/>
+      <c r="Q20" s="32">
         <v>5</v>
       </c>
-      <c r="R20" s="41" t="s">
+      <c r="R20" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="33">
+      <c r="S20" s="45"/>
+      <c r="T20" s="45"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B21" s="32">
         <v>13</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="54"/>
-      <c r="Q21" s="33">
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="56"/>
+      <c r="Q21" s="32">
         <v>6</v>
       </c>
-      <c r="R21" s="41" t="s">
+      <c r="R21" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B22" s="33">
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B22" s="32">
         <v>14</v>
       </c>
-      <c r="C22" s="42" t="s">
+      <c r="C22" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="54"/>
-      <c r="Q22" s="33">
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="56"/>
+      <c r="Q22" s="32">
         <v>7</v>
       </c>
-      <c r="R22" s="40" t="s">
+      <c r="R22" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B23" s="33">
+      <c r="S22" s="45"/>
+      <c r="T22" s="45"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B23" s="32">
         <v>15</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="54"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="55"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="56"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="57"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="56"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="I24" s="57"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="R19:T19"/>
     <mergeCell ref="C23:E23"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
@@ -2904,12 +2898,18 @@
     <mergeCell ref="I6:O6"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2923,203 +2923,203 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:AC17"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="4" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="3" max="4" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" customWidth="1"/>
+    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="6.1640625" customWidth="1"/>
+    <col min="12" max="12" width="6.5" customWidth="1"/>
     <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" customWidth="1"/>
-    <col min="16" max="17" width="8.88671875" customWidth="1"/>
-    <col min="22" max="22" width="9.109375" customWidth="1"/>
-    <col min="23" max="25" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.83203125" customWidth="1"/>
+    <col min="16" max="17" width="8.83203125" customWidth="1"/>
+    <col min="22" max="22" width="9.1640625" customWidth="1"/>
+    <col min="23" max="25" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
-      <c r="B3" s="60" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B3" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B5" s="9"/>
     </row>
-    <row r="6" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="61" t="s">
+    <row r="6" spans="2:29" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="61" t="s">
+      <c r="E6" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="61"/>
-      <c r="U6" s="61"/>
-      <c r="V6" s="61"/>
-      <c r="W6" s="61"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="61"/>
-      <c r="Z6" s="61"/>
-      <c r="AA6" s="61"/>
-      <c r="AB6" s="61"/>
-      <c r="AC6" s="61"/>
-    </row>
-    <row r="7" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="71" t="s">
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+      <c r="Z6" s="71"/>
+      <c r="AA6" s="71"/>
+      <c r="AB6" s="71"/>
+      <c r="AC6" s="71"/>
+    </row>
+    <row r="7" spans="2:29" ht="16" x14ac:dyDescent="0.2">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="68" t="s">
+      <c r="F7" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="65" t="s">
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="65"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="65"/>
-      <c r="U7" s="65"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="64" t="s">
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="66"/>
+      <c r="U7" s="66"/>
+      <c r="V7" s="66"/>
+      <c r="W7" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="64"/>
-      <c r="AA7" s="64"/>
-      <c r="AB7" s="64"/>
-      <c r="AC7" s="64"/>
-    </row>
-    <row r="8" spans="2:29" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="61"/>
-      <c r="C8" s="66" t="s">
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="67"/>
+      <c r="AC7" s="67"/>
+    </row>
+    <row r="8" spans="2:29" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="71"/>
+      <c r="C8" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="68" t="s">
+      <c r="E8" s="65"/>
+      <c r="F8" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68" t="s">
+      <c r="G8" s="64"/>
+      <c r="H8" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68" t="s">
+      <c r="I8" s="64"/>
+      <c r="J8" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68" t="s">
+      <c r="K8" s="64"/>
+      <c r="L8" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68" t="s">
+      <c r="M8" s="64"/>
+      <c r="N8" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="O8" s="68"/>
-      <c r="P8" s="65" t="s">
+      <c r="O8" s="64"/>
+      <c r="P8" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="Q8" s="65" t="s">
+      <c r="Q8" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="R8" s="65" t="s">
+      <c r="R8" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="S8" s="65" t="s">
+      <c r="S8" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="T8" s="65" t="s">
+      <c r="T8" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="U8" s="65" t="s">
+      <c r="U8" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="V8" s="65" t="s">
+      <c r="V8" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="W8" s="69">
+      <c r="W8" s="68">
         <v>0</v>
       </c>
-      <c r="X8" s="64">
+      <c r="X8" s="67">
         <v>1</v>
       </c>
-      <c r="Y8" s="64">
+      <c r="Y8" s="67">
         <v>2</v>
       </c>
-      <c r="Z8" s="64" t="s">
+      <c r="Z8" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="AA8" s="64" t="s">
+      <c r="AA8" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="AB8" s="64" t="s">
+      <c r="AB8" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="AC8" s="64" t="s">
+      <c r="AC8" s="67" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="61"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="71"/>
+    <row r="9" spans="2:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="71"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="65"/>
       <c r="F9" s="11" t="s">
         <v>45</v>
       </c>
@@ -3150,22 +3150,22 @@
       <c r="O9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="65"/>
-      <c r="R9" s="65"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="65"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="65"/>
-      <c r="W9" s="70"/>
-      <c r="X9" s="64"/>
-      <c r="Y9" s="64"/>
-      <c r="Z9" s="64"/>
-      <c r="AA9" s="64"/>
-      <c r="AB9" s="64"/>
-      <c r="AC9" s="64"/>
-    </row>
-    <row r="10" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66"/>
+      <c r="U9" s="66"/>
+      <c r="V9" s="66"/>
+      <c r="W9" s="69"/>
+      <c r="X9" s="67"/>
+      <c r="Y9" s="67"/>
+      <c r="Z9" s="67"/>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="67"/>
+      <c r="AC9" s="67"/>
+    </row>
+    <row r="10" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>47</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="AB10" s="17"/>
       <c r="AC10" s="17"/>
     </row>
-    <row r="11" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
         <v>48</v>
       </c>
@@ -3255,14 +3255,14 @@
       <c r="AB11" s="17"/>
       <c r="AC11" s="17"/>
     </row>
-    <row r="12" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B12" s="12">
         <v>3</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="39" t="b">
+      <c r="D12" s="38" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="14" t="s">
@@ -3303,7 +3303,7 @@
       <c r="AB12" s="17"/>
       <c r="AC12" s="17"/>
     </row>
-    <row r="13" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="12">
         <v>4</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="AB13" s="17"/>
       <c r="AC13" s="17"/>
     </row>
-    <row r="14" spans="2:29" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B14" s="12">
         <v>5</v>
       </c>
@@ -3405,7 +3405,7 @@
       <c r="AB14" s="17"/>
       <c r="AC14" s="17"/>
     </row>
-    <row r="15" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:29" ht="17" x14ac:dyDescent="0.2">
       <c r="B15" s="12">
         <v>6</v>
       </c>
@@ -3457,7 +3457,7 @@
       <c r="AB15" s="17"/>
       <c r="AC15" s="17"/>
     </row>
-    <row r="16" spans="2:29" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:29" ht="34" x14ac:dyDescent="0.2">
       <c r="B16" s="12">
         <v>7</v>
       </c>
@@ -3509,26 +3509,11 @@
       </c>
       <c r="AC16" s="17"/>
     </row>
-    <row r="17" spans="2:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:V7"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="U8:U9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -3545,6 +3530,21 @@
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="T8:T9"/>
     <mergeCell ref="W7:AC7"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:V7"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3558,72 +3558,72 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" customWidth="1"/>
-    <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" customWidth="1"/>
+    <col min="13" max="13" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B1" s="10"/>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="74" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B3" s="95" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="75" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B4" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="106" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="E4" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="78"/>
-      <c r="K4" s="77" t="s">
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="78"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="76"/>
-      <c r="C5" s="85"/>
-      <c r="D5" s="87"/>
+      <c r="L4" s="99"/>
+    </row>
+    <row r="5" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="97"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="107"/>
       <c r="E5" s="2" t="s">
         <v>132</v>
       </c>
@@ -3634,8 +3634,8 @@
         <v>134</v>
       </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="80"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="101"/>
       <c r="K5" s="2" t="s">
         <v>55</v>
       </c>
@@ -3643,11 +3643,11 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B6" s="19">
         <v>9</v>
       </c>
-      <c r="C6" s="81" t="s">
+      <c r="C6" s="102" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -3663,8 +3663,8 @@
         <v>136</v>
       </c>
       <c r="H6" s="20"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="89"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="109"/>
       <c r="K6" s="20" t="b">
         <v>0</v>
       </c>
@@ -3672,11 +3672,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="19">
         <v>10</v>
       </c>
-      <c r="C7" s="81"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="4" t="s">
         <v>58</v>
       </c>
@@ -3690,8 +3690,8 @@
         <v>136</v>
       </c>
       <c r="H7" s="19"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="78"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
       <c r="K7" s="19" t="b">
         <v>1</v>
       </c>
@@ -3699,11 +3699,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="19">
         <v>11</v>
       </c>
-      <c r="C8" s="81"/>
+      <c r="C8" s="102"/>
       <c r="D8" s="4" t="s">
         <v>128</v>
       </c>
@@ -3717,8 +3717,8 @@
         <v>136</v>
       </c>
       <c r="H8" s="19"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="78"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="99"/>
       <c r="K8" s="19" t="b">
         <v>1</v>
       </c>
@@ -3726,11 +3726,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="19">
         <v>12</v>
       </c>
-      <c r="C9" s="81"/>
+      <c r="C9" s="102"/>
       <c r="D9" s="4" t="s">
         <v>129</v>
       </c>
@@ -3744,8 +3744,8 @@
         <v>0</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="78"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="99"/>
       <c r="K9" s="19" t="b">
         <v>0</v>
       </c>
@@ -3753,65 +3753,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B10" s="110">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="39">
         <v>13</v>
       </c>
-      <c r="C10" s="81"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="110">
+      <c r="E10" s="39">
         <v>1</v>
       </c>
-      <c r="F10" s="110">
+      <c r="F10" s="39">
         <v>10</v>
       </c>
-      <c r="G10" s="110">
+      <c r="G10" s="39">
         <v>5</v>
       </c>
-      <c r="H10" s="110"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="110" t="b">
+      <c r="H10" s="39"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="39" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="110" t="b">
+      <c r="L10" s="39" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="110">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="39">
         <v>14</v>
       </c>
-      <c r="C11" s="81"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="E11" s="110">
+      <c r="E11" s="39">
         <v>1</v>
       </c>
-      <c r="F11" s="110">
+      <c r="F11" s="39">
         <v>5</v>
       </c>
-      <c r="G11" s="110">
+      <c r="G11" s="39">
         <v>20</v>
       </c>
-      <c r="H11" s="110"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="112"/>
-      <c r="K11" s="110" t="b">
+      <c r="H11" s="39"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="L11" s="110" t="b">
+      <c r="L11" s="39" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>15</v>
       </c>
-      <c r="C12" s="82"/>
+      <c r="C12" s="103"/>
       <c r="D12" s="4" t="s">
         <v>137</v>
       </c>
@@ -3825,8 +3825,8 @@
         <v>139</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="80"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="101"/>
       <c r="K12" s="2" t="b">
         <v>1</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -3847,93 +3847,93 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="K14" s="21"/>
     </row>
-    <row r="15" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="90" t="s">
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="91"/>
-      <c r="H15" s="72" t="s">
+      <c r="G15" s="111"/>
+      <c r="H15" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="100" t="s">
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="N15" s="101"/>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="109" t="s">
+      <c r="N15" s="86"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="104" t="s">
+      <c r="D16" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="102" t="s">
+      <c r="E16" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="108" t="s">
+      <c r="F16" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="106" t="s">
+      <c r="G16" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="105" t="s">
+      <c r="H16" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="I16" s="104" t="s">
+      <c r="I16" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="104" t="s">
+      <c r="J16" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="104" t="s">
+      <c r="K16" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="L16" s="96" t="s">
+      <c r="L16" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="M16" s="98" t="s">
+      <c r="M16" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="N16" s="84" t="s">
+      <c r="N16" s="89" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="99"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="107"/>
-      <c r="H17" s="93"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="97"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="92"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B17" s="81"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="88"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="75"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B18" s="24">
         <v>7</v>
       </c>
       <c r="C18" s="22">
@@ -3942,8 +3942,10 @@
       <c r="D18" s="22">
         <v>0</v>
       </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24">
+      <c r="E18" s="112">
+        <v>1</v>
+      </c>
+      <c r="F18" s="23">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -3952,42 +3954,27 @@
       <c r="H18" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="24">
         <f>SUM(J18:K18)</f>
         <v>0</v>
       </c>
       <c r="J18" s="22">
         <v>0</v>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="25">
         <v>0</v>
       </c>
-      <c r="L18" s="27"/>
+      <c r="L18" s="26"/>
       <c r="M18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="N18" s="28">
+      <c r="N18" s="27">
         <f>C18</f>
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="L16:L17"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:L3"/>
@@ -4004,6 +3991,21 @@
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4012,12 +4014,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4210,20 +4214,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="301f98df-4edd-4096-94f8-2f8af3eee570">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
+    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4248,12 +4253,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA2F5940-EC19-4D08-A8C2-FA31EF734077}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EECFCB93-350B-4228-B7F4-DB12383611F2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="301f98df-4edd-4096-94f8-2f8af3eee570"/>
-    <ds:schemaRef ds:uri="cbfc0213-1ef7-4e52-9599-c30bc1b3f3d7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>